--- a/src/evaluation/data/processed/nearest_hospitals_to_sample_points.xlsx
+++ b/src/evaluation/data/processed/nearest_hospitals_to_sample_points.xlsx
@@ -473,7 +473,7 @@
         <v>6.782133043333384</v>
       </c>
       <c r="D2" t="n">
-        <v>49.257259</v>
+        <v>49.25726</v>
       </c>
       <c r="E2" t="n">
         <v>6.852541</v>
@@ -495,13 +495,13 @@
         <v>6.923982130000041</v>
       </c>
       <c r="D3" t="n">
-        <v>49.26812930661734</v>
+        <v>49.27695</v>
       </c>
       <c r="E3" t="n">
-        <v>6.929470619593767</v>
+        <v>6.870121</v>
       </c>
       <c r="F3" t="n">
-        <v>2.377</v>
+        <v>4.149</v>
       </c>
     </row>
     <row r="4">
@@ -517,13 +517,13 @@
         <v>6.994906673333371</v>
       </c>
       <c r="D4" t="n">
-        <v>49.237085</v>
+        <v>49.23709</v>
       </c>
       <c r="E4" t="n">
         <v>6.99259</v>
       </c>
       <c r="F4" t="n">
-        <v>0.892</v>
+        <v>0.891</v>
       </c>
     </row>
     <row r="5">
@@ -539,13 +539,13 @@
         <v>7.065831216666699</v>
       </c>
       <c r="D5" t="n">
-        <v>49.153009</v>
+        <v>49.15301</v>
       </c>
       <c r="E5" t="n">
         <v>7.048336</v>
       </c>
       <c r="F5" t="n">
-        <v>1.334</v>
+        <v>1.333</v>
       </c>
     </row>
     <row r="6">
@@ -561,7 +561,7 @@
         <v>7.065831216666699</v>
       </c>
       <c r="D6" t="n">
-        <v>49.297734</v>
+        <v>49.29773</v>
       </c>
       <c r="E6" t="n">
         <v>7.054714</v>
@@ -583,7 +583,7 @@
         <v>6.457994543833375</v>
       </c>
       <c r="D7" t="n">
-        <v>49.495769</v>
+        <v>49.49577</v>
       </c>
       <c r="E7" t="n">
         <v>6.596771</v>
@@ -605,7 +605,7 @@
         <v>6.558694497666711</v>
       </c>
       <c r="D8" t="n">
-        <v>49.495769</v>
+        <v>49.49577</v>
       </c>
       <c r="E8" t="n">
         <v>6.596771</v>
@@ -627,7 +627,7 @@
         <v>6.659394451500049</v>
       </c>
       <c r="D9" t="n">
-        <v>49.457186</v>
+        <v>49.45719</v>
       </c>
       <c r="E9" t="n">
         <v>6.631578</v>
@@ -649,13 +649,13 @@
         <v>6.760094405333386</v>
       </c>
       <c r="D10" t="n">
-        <v>49.457186</v>
+        <v>49.49195</v>
       </c>
       <c r="E10" t="n">
-        <v>6.631578</v>
+        <v>6.843934</v>
       </c>
       <c r="F10" t="n">
-        <v>10.122</v>
+        <v>6.075</v>
       </c>
     </row>
     <row r="11">
@@ -671,7 +671,7 @@
         <v>6.860794359166722</v>
       </c>
       <c r="D11" t="n">
-        <v>49.537868</v>
+        <v>49.53787</v>
       </c>
       <c r="E11" t="n">
         <v>6.88934</v>
@@ -693,13 +693,13 @@
         <v>6.980411860000051</v>
       </c>
       <c r="D12" t="n">
-        <v>49.33767769818895</v>
+        <v>49.41257</v>
       </c>
       <c r="E12" t="n">
-        <v>7.005279273288449</v>
+        <v>6.909871</v>
       </c>
       <c r="F12" t="n">
-        <v>3.439</v>
+        <v>7.445</v>
       </c>
     </row>
     <row r="13">
@@ -715,13 +715,13 @@
         <v>7.04284978800005</v>
       </c>
       <c r="D13" t="n">
-        <v>49.33767769818895</v>
+        <v>49.40381</v>
       </c>
       <c r="E13" t="n">
-        <v>7.005279273288449</v>
+        <v>7.107757</v>
       </c>
       <c r="F13" t="n">
-        <v>6.382</v>
+        <v>4.971</v>
       </c>
     </row>
     <row r="14">
@@ -737,13 +737,13 @@
         <v>7.105287716000049</v>
       </c>
       <c r="D14" t="n">
-        <v>49.40973615864516</v>
+        <v>49.40381</v>
       </c>
       <c r="E14" t="n">
-        <v>7.172516962777409</v>
+        <v>7.107757</v>
       </c>
       <c r="F14" t="n">
-        <v>4.915</v>
+        <v>1.269</v>
       </c>
     </row>
     <row r="15">
@@ -759,13 +759,13 @@
         <v>7.167725644000048</v>
       </c>
       <c r="D15" t="n">
-        <v>49.40973615864516</v>
+        <v>49.40381</v>
       </c>
       <c r="E15" t="n">
-        <v>7.172516962777409</v>
+        <v>7.107757</v>
       </c>
       <c r="F15" t="n">
-        <v>2.272</v>
+        <v>4.633</v>
       </c>
     </row>
     <row r="16">
@@ -781,13 +781,13 @@
         <v>7.230163572000047</v>
       </c>
       <c r="D16" t="n">
-        <v>49.39718981222195</v>
+        <v>49.45466</v>
       </c>
       <c r="E16" t="n">
-        <v>7.213364346793378</v>
+        <v>7.186793</v>
       </c>
       <c r="F16" t="n">
-        <v>2.336</v>
+        <v>5.408</v>
       </c>
     </row>
     <row r="17">
@@ -803,7 +803,7 @@
         <v>6.612956306666717</v>
       </c>
       <c r="D17" t="n">
-        <v>49.266127</v>
+        <v>49.26613</v>
       </c>
       <c r="E17" t="n">
         <v>6.68297</v>
@@ -825,7 +825,7 @@
         <v>6.688228945333378</v>
       </c>
       <c r="D18" t="n">
-        <v>49.328624</v>
+        <v>49.32862</v>
       </c>
       <c r="E18" t="n">
         <v>6.714977</v>
@@ -847,7 +847,7 @@
         <v>6.763501584000039</v>
       </c>
       <c r="D19" t="n">
-        <v>49.315236</v>
+        <v>49.31524</v>
       </c>
       <c r="E19" t="n">
         <v>6.756487</v>
@@ -869,13 +869,13 @@
         <v>6.8387742226667</v>
       </c>
       <c r="D20" t="n">
-        <v>49.35666769333056</v>
+        <v>49.41909</v>
       </c>
       <c r="E20" t="n">
-        <v>6.822620825380222</v>
+        <v>6.88979</v>
       </c>
       <c r="F20" t="n">
-        <v>1.204</v>
+        <v>7.633</v>
       </c>
     </row>
     <row r="21">
@@ -891,13 +891,13 @@
         <v>6.914046861333361</v>
       </c>
       <c r="D21" t="n">
-        <v>49.44208949482798</v>
+        <v>49.41909</v>
       </c>
       <c r="E21" t="n">
-        <v>6.904224529034402</v>
+        <v>6.88979</v>
       </c>
       <c r="F21" t="n">
-        <v>1.52</v>
+        <v>4.279</v>
       </c>
     </row>
     <row r="22">
@@ -913,7 +913,7 @@
         <v>7.119161333333362</v>
       </c>
       <c r="D22" t="n">
-        <v>49.153009</v>
+        <v>49.15301</v>
       </c>
       <c r="E22" t="n">
         <v>7.048336</v>
@@ -935,13 +935,13 @@
         <v>7.175744166666694</v>
       </c>
       <c r="D23" t="n">
-        <v>49.290552</v>
+        <v>49.26165</v>
       </c>
       <c r="E23" t="n">
-        <v>7.113175</v>
+        <v>7.252301</v>
       </c>
       <c r="F23" t="n">
-        <v>9.785</v>
+        <v>7.794</v>
       </c>
     </row>
     <row r="24">
@@ -957,13 +957,13 @@
         <v>7.232327000000026</v>
       </c>
       <c r="D24" t="n">
-        <v>49.317756</v>
+        <v>49.26165</v>
       </c>
       <c r="E24" t="n">
-        <v>7.227015</v>
+        <v>7.252301</v>
       </c>
       <c r="F24" t="n">
-        <v>6.261</v>
+        <v>1.454</v>
       </c>
     </row>
     <row r="25">
@@ -979,7 +979,7 @@
         <v>7.288909833333359</v>
       </c>
       <c r="D25" t="n">
-        <v>49.317756</v>
+        <v>49.31776</v>
       </c>
       <c r="E25" t="n">
         <v>7.227015</v>
@@ -1001,13 +1001,13 @@
         <v>7.345492666666691</v>
       </c>
       <c r="D26" t="n">
-        <v>49.3762045599062</v>
+        <v>49.3082</v>
       </c>
       <c r="E26" t="n">
-        <v>7.280034712412421</v>
+        <v>7.351777</v>
       </c>
       <c r="F26" t="n">
-        <v>5.111</v>
+        <v>5.706</v>
       </c>
     </row>
     <row r="27">
@@ -1023,13 +1023,13 @@
         <v>6.960983777333401</v>
       </c>
       <c r="D27" t="n">
-        <v>49.537868</v>
+        <v>49.56781</v>
       </c>
       <c r="E27" t="n">
-        <v>6.88934</v>
+        <v>6.961946</v>
       </c>
       <c r="F27" t="n">
-        <v>5.393</v>
+        <v>4.809</v>
       </c>
     </row>
     <row r="28">
@@ -1045,13 +1045,13 @@
         <v>7.030513554666736</v>
       </c>
       <c r="D28" t="n">
-        <v>49.537868</v>
+        <v>49.54908</v>
       </c>
       <c r="E28" t="n">
-        <v>6.88934</v>
+        <v>7.107687</v>
       </c>
       <c r="F28" t="n">
-        <v>10.326</v>
+        <v>6.215</v>
       </c>
     </row>
     <row r="29">
@@ -1067,13 +1067,13 @@
         <v>7.10004333200007</v>
       </c>
       <c r="D29" t="n">
-        <v>49.453979</v>
+        <v>49.54908</v>
       </c>
       <c r="E29" t="n">
-        <v>7.178492</v>
+        <v>7.107687</v>
       </c>
       <c r="F29" t="n">
-        <v>9.693</v>
+        <v>2.781</v>
       </c>
     </row>
     <row r="30">
@@ -1089,13 +1089,13 @@
         <v>7.169573109333403</v>
       </c>
       <c r="D30" t="n">
-        <v>49.454659</v>
+        <v>49.54908</v>
       </c>
       <c r="E30" t="n">
-        <v>7.186793</v>
+        <v>7.107687</v>
       </c>
       <c r="F30" t="n">
-        <v>7.876</v>
+        <v>5.243</v>
       </c>
     </row>
     <row r="31">
@@ -1111,13 +1111,13 @@
         <v>7.239102886666738</v>
       </c>
       <c r="D31" t="n">
-        <v>49.454659</v>
+        <v>49.54908</v>
       </c>
       <c r="E31" t="n">
-        <v>7.186793</v>
+        <v>7.107687</v>
       </c>
       <c r="F31" t="n">
-        <v>12.617</v>
+        <v>9.631</v>
       </c>
     </row>
   </sheetData>
